--- a/nodes_source_analyses/energy/energy/energy_production_methanol_synthesis_synthetic.xlsx
+++ b/nodes_source_analyses/energy/energy/energy_production_methanol_synthesis_synthetic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10510"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyradehaan/github/etdataset/nodes_source_analyses/energy/energy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87D1069-9B52-4647-AF1C-C00849F6618E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F28152D-F8ED-1C44-82B2-D8CF762609C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" tabRatio="762" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="762" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover sheet" sheetId="14" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="135">
   <si>
     <t>Source</t>
   </si>
@@ -496,15 +496,49 @@
   <si>
     <t>energy_production_methanol_synthetis_synthetic</t>
   </si>
+  <si>
+    <t>EMISSIONS (Non-fuel/energy-related emissions or emissions reductions (e.g. CCS</t>
+  </si>
+  <si>
+    <t>CO2 input</t>
+  </si>
+  <si>
+    <t>Mton/PJ product</t>
+  </si>
+  <si>
+    <t>kg/MJ product</t>
+  </si>
+  <si>
+    <t>CO2 output</t>
+  </si>
+  <si>
+    <t>CO2 utilised</t>
+  </si>
+  <si>
+    <t>CO2 input is 0.074 Mton in 2020. Not all ends up in methanol as part is ending up, partly after conversion, as CO2 emissions in the flue gas</t>
+  </si>
+  <si>
+    <t>co2_utilisation_per_mj</t>
+  </si>
+  <si>
+    <t>kg CO2/MJ</t>
+  </si>
+  <si>
+    <t>CO2 utilisation per MJ product output</t>
+  </si>
+  <si>
+    <t>kgCO2/MJ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="36">
     <font>
@@ -832,7 +866,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1063,6 +1097,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="496">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1562,7 +1611,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1807,6 +1856,17 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="496">
@@ -2368,23 +2428,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>362857</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>175664</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>216476</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>814934</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>76006</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>389659</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>132950</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5CD4E3D-17B9-5A3F-8210-84F2972DF460}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1BD5AA9-FE03-AB41-B422-1ECB256D6D0A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2400,8 +2460,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9701092" y="4433899"/>
-          <a:ext cx="17335607" cy="18907653"/>
+          <a:off x="9322955" y="5397499"/>
+          <a:ext cx="10737272" cy="13756587"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2416,6 +2476,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover Sheet"/>
       <sheetName val="Changelog"/>
@@ -2529,6 +2592,9 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Title"/>
       <sheetName val="Description"/>
@@ -2913,12 +2979,12 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="29" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="21" customWidth="1"/>
-    <col min="3" max="3" width="38.42578125" style="21" customWidth="1"/>
-    <col min="4" max="16384" width="10.85546875" style="21"/>
+    <col min="1" max="1" width="3.5" style="29" customWidth="1"/>
+    <col min="2" max="2" width="11.5" style="21" customWidth="1"/>
+    <col min="3" max="3" width="38.5" style="21" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="27" customFormat="1">
@@ -3090,18 +3156,18 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A2:K42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <dimension ref="A2:K43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="3.42578125" style="33" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" style="33" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="33" customWidth="1"/>
-    <col min="6" max="6" width="4.42578125" style="33" customWidth="1"/>
-    <col min="7" max="7" width="49.42578125" style="33" customWidth="1"/>
-    <col min="8" max="8" width="20.85546875" style="33" customWidth="1"/>
-    <col min="9" max="9" width="42.42578125" style="33" customWidth="1"/>
-    <col min="10" max="10" width="5.42578125" style="33" customWidth="1"/>
-    <col min="11" max="16384" width="10.85546875" style="33"/>
+    <col min="1" max="2" width="3.5" style="33" customWidth="1"/>
+    <col min="3" max="3" width="51.5" style="33" customWidth="1"/>
+    <col min="4" max="5" width="14.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="4.5" style="33" customWidth="1"/>
+    <col min="7" max="7" width="49.5" style="33" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" style="33" customWidth="1"/>
+    <col min="9" max="9" width="42.5" style="33" customWidth="1"/>
+    <col min="10" max="10" width="5.5" style="33" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="33"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:11">
@@ -3515,27 +3581,38 @@
     </row>
     <row r="32" spans="1:10" ht="17" thickBot="1">
       <c r="A32" s="88"/>
-      <c r="B32" s="94"/>
-      <c r="C32" s="95"/>
-      <c r="D32" s="95"/>
-      <c r="E32" s="95"/>
-      <c r="F32" s="95"/>
-      <c r="G32" s="95"/>
-      <c r="H32" s="95"/>
-      <c r="I32" s="95"/>
-      <c r="J32" s="96"/>
-    </row>
-    <row r="33" spans="1:10">
+      <c r="B32" s="89"/>
+      <c r="C32" s="166" t="s">
+        <v>131</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E32" s="167">
+        <f>'Research data'!H26</f>
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="F32" s="166"/>
+      <c r="G32" s="166" t="s">
+        <v>133</v>
+      </c>
+      <c r="H32" s="166"/>
+      <c r="I32" s="118" t="s">
+        <v>99</v>
+      </c>
+      <c r="J32" s="90"/>
+    </row>
+    <row r="33" spans="1:10" ht="17" thickBot="1">
       <c r="A33" s="88"/>
-      <c r="B33" s="88"/>
-      <c r="C33" s="88"/>
-      <c r="D33" s="88"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="88"/>
-      <c r="H33" s="88"/>
-      <c r="I33" s="88"/>
-      <c r="J33" s="88"/>
+      <c r="B33" s="94"/>
+      <c r="C33" s="95"/>
+      <c r="D33" s="95"/>
+      <c r="E33" s="95"/>
+      <c r="F33" s="95"/>
+      <c r="G33" s="95"/>
+      <c r="H33" s="95"/>
+      <c r="I33" s="95"/>
+      <c r="J33" s="96"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="88"/>
@@ -3564,6 +3641,8 @@
     <row r="36" spans="1:10">
       <c r="A36" s="88"/>
       <c r="B36" s="88"/>
+      <c r="C36" s="88"/>
+      <c r="D36" s="88"/>
       <c r="E36" s="88"/>
       <c r="F36" s="88"/>
       <c r="G36" s="88"/>
@@ -3574,8 +3653,6 @@
     <row r="37" spans="1:10">
       <c r="A37" s="88"/>
       <c r="B37" s="88"/>
-      <c r="C37" s="88"/>
-      <c r="D37" s="88"/>
       <c r="E37" s="88"/>
       <c r="F37" s="88"/>
       <c r="G37" s="88"/>
@@ -3621,9 +3698,21 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="88"/>
+      <c r="B41" s="88"/>
+      <c r="C41" s="88"/>
+      <c r="D41" s="88"/>
+      <c r="E41" s="88"/>
+      <c r="F41" s="88"/>
+      <c r="G41" s="88"/>
+      <c r="H41" s="88"/>
+      <c r="I41" s="88"/>
+      <c r="J41" s="88"/>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="88"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3639,25 +3728,25 @@
   <sheetPr codeName="Sheet3">
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A2:P25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <dimension ref="A2:P26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="39" customWidth="1"/>
+    <col min="1" max="1" width="3.5" style="39" customWidth="1"/>
     <col min="2" max="2" width="3" style="39" customWidth="1"/>
     <col min="3" max="3" width="61" style="39" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="39" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="39" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="39" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="39" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="39" customWidth="1"/>
     <col min="7" max="7" width="3" style="39" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="39" customWidth="1"/>
-    <col min="9" max="9" width="2.42578125" style="39" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="39" customWidth="1"/>
-    <col min="11" max="12" width="2.42578125" style="39" customWidth="1"/>
-    <col min="13" max="13" width="23.42578125" style="39" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" style="39" customWidth="1"/>
+    <col min="9" max="9" width="2.5" style="39" customWidth="1"/>
+    <col min="10" max="10" width="13.5" style="39" customWidth="1"/>
+    <col min="11" max="12" width="2.5" style="39" customWidth="1"/>
+    <col min="13" max="13" width="23.5" style="39" customWidth="1"/>
     <col min="14" max="14" width="11" style="39" customWidth="1"/>
-    <col min="15" max="15" width="2.42578125" style="39" customWidth="1"/>
-    <col min="16" max="16" width="22.42578125" style="39" customWidth="1"/>
-    <col min="17" max="16384" width="10.85546875" style="39"/>
+    <col min="15" max="15" width="2.5" style="39" customWidth="1"/>
+    <col min="16" max="16" width="22.5" style="39" customWidth="1"/>
+    <col min="17" max="16384" width="10.83203125" style="39"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="17" thickBot="1"/>
@@ -4136,6 +4225,23 @@
       <c r="L25" s="98"/>
       <c r="M25" s="105"/>
     </row>
+    <row r="26" spans="1:13" ht="17" thickBot="1">
+      <c r="C26" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" s="168" t="s">
+        <v>134</v>
+      </c>
+      <c r="H26" s="169">
+        <f>ROUND(J26,5)</f>
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="I26" s="98"/>
+      <c r="J26" s="136">
+        <f>Notes!F43</f>
+        <v>7.3999999999999996E-2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -4148,19 +4254,19 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="B1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.1640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="48" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="48" customWidth="1"/>
-    <col min="3" max="3" width="24.42578125" style="48" customWidth="1"/>
-    <col min="4" max="4" width="32.85546875" style="48" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" style="48" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="48" customWidth="1"/>
+    <col min="1" max="1" width="3.5" style="48" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="48" customWidth="1"/>
+    <col min="3" max="3" width="24.5" style="48" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" style="48" customWidth="1"/>
+    <col min="5" max="5" width="6.1640625" style="48" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="48" customWidth="1"/>
     <col min="7" max="7" width="78" style="48" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="52" customWidth="1"/>
-    <col min="9" max="9" width="31.42578125" style="52" customWidth="1"/>
-    <col min="10" max="10" width="98.42578125" style="48" customWidth="1"/>
-    <col min="11" max="16384" width="33.140625" style="48"/>
+    <col min="8" max="8" width="12.5" style="52" customWidth="1"/>
+    <col min="9" max="9" width="31.5" style="52" customWidth="1"/>
+    <col min="10" max="10" width="98.5" style="48" customWidth="1"/>
+    <col min="11" max="16384" width="33.1640625" style="48"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="17" thickBot="1"/>
@@ -4286,19 +4392,19 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <dimension ref="A1:N49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="3.42578125" style="55" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="55" customWidth="1"/>
-    <col min="4" max="4" width="7.140625" style="55" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" style="55" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" style="55" customWidth="1"/>
-    <col min="7" max="13" width="10.85546875" style="55"/>
-    <col min="14" max="14" width="15.7109375" style="55" customWidth="1"/>
-    <col min="15" max="15" width="10.85546875" style="55"/>
-    <col min="16" max="16" width="12.140625" style="55" customWidth="1"/>
-    <col min="17" max="16384" width="10.85546875" style="55"/>
+    <col min="1" max="2" width="3.5" style="55" customWidth="1"/>
+    <col min="3" max="3" width="18.5" style="55" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" style="55" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="55" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" style="55" customWidth="1"/>
+    <col min="7" max="13" width="10.83203125" style="55"/>
+    <col min="14" max="14" width="15.6640625" style="55" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" style="55"/>
+    <col min="16" max="16" width="12.1640625" style="55" customWidth="1"/>
+    <col min="17" max="16384" width="10.83203125" style="55"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17" thickBot="1"/>
@@ -4743,6 +4849,74 @@
       <c r="A39" s="59"/>
       <c r="B39" s="134"/>
     </row>
+    <row r="41" spans="1:8">
+      <c r="E41" s="59" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="E42" s="55" t="s">
+        <v>125</v>
+      </c>
+      <c r="F42" s="163">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="G42" s="55" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="F43" s="153">
+        <f>F42*1000000000/1000000000</f>
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="G43" s="55" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="E44" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="F44" s="164">
+        <v>0.01</v>
+      </c>
+      <c r="G44" s="55" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="F45" s="55">
+        <f>F44</f>
+        <v>0.01</v>
+      </c>
+      <c r="G45" s="55" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="E46" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="F46" s="153">
+        <f>F42-F44</f>
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="G46" s="55" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="F47" s="145"/>
+    </row>
+    <row r="48" spans="1:8" ht="102">
+      <c r="E48" s="165" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49" spans="6:6">
+      <c r="F49" s="145"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
